--- a/003_Gene_Synthesis_Hub/python-app/Databases/Vector_database.xlsx
+++ b/003_Gene_Synthesis_Hub/python-app/Databases/Vector_database.xlsx
@@ -551,10 +551,10 @@
     <t>Box Position</t>
   </si>
   <si>
-    <t>Vector Name</t>
-  </si>
-  <si>
-    <t>Emzymes cut</t>
+    <t>Vector</t>
+  </si>
+  <si>
+    <t>Digestion</t>
   </si>
   <si>
     <t>Lot</t>
